--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Area Under Cultivation - Major Commercial Crops.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Area Under Cultivation - Major Commercial Crops.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>Year</t>
   </si>
@@ -283,14 +283,14 @@
     <t>( Lakhs Hectares )</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :  1. Data for 2025-26 are based on First Advance Estimates.
-             2. Data for 1960-61 to 1969-70 relate to total of five major oilseeds,viz., groundnut, castorseed, sesamum, rapeseed and mustard, and linseed.
-             3. Data for 1950-51 and 1951-52 under the head Raw Jute &amp; Mesta
-             4. Oilseed data comprises total for nine oilseeds out of the eleven in all.
-             5. Tea and coffee area data is provisional.
-             6. -: Not Available.     
-Also see Notes on Tables.
-Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
+    <t xml:space="preserve">Notes    : 1. Data for 2025-26 are based on Third Advance Estimates.
+               2. Data for 1969-70 relate to total of five major oilseeds, viz., groundnut, castorseed, sesamum, rapeseed and mustard, and linseed. 
+               3. Oilseed data comprises total for nine oilseeds out of the eleven in all. 
+               4. -: Not Available. 
+               5. Tea and coffee area data is provisional. 
+                 Also see Notes on Tables.
+Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India; Tea Board of India; and Coffee Board of India
+</t>
   </si>
 </sst>
 </file>
@@ -522,12 +522,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:M87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.5455986666667" customWidth="1"/>
     <col min="3" max="12" width="11.4083986666667" customWidth="1"/>
     <col min="13" max="13" width="95632e-6" customWidth="1"/>
+    <col min="14" max="14" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -641,31 +642,31 @@
         <v>12</v>
       </c>
       <c r="C9" s="10">
-        <v>47.21</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>13</v>
+        <v>58.67</v>
+      </c>
+      <c r="D9" s="10">
+        <v>94.27</v>
       </c>
       <c r="E9" s="10">
-        <v>123.53</v>
+        <v>123.86</v>
       </c>
       <c r="F9" s="10">
-        <v>191.1</v>
+        <v>308.86</v>
       </c>
       <c r="G9" s="10">
-        <v>56.93</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>13</v>
+        <v>58.84</v>
+      </c>
+      <c r="H9" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="I9" s="10">
+        <v>4.9</v>
       </c>
       <c r="J9" s="10">
-        <v>110.86</v>
+        <v>115.25</v>
       </c>
       <c r="K9" s="10">
-        <v>5.46</v>
+        <v>6.06</v>
       </c>
       <c r="L9" s="11" t="s">
         <v>13</v>
@@ -691,7 +692,7 @@
         <v>54.5</v>
       </c>
       <c r="H10" s="12">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I10" s="12">
         <v>4.9</v>
@@ -3313,6 +3314,7 @@
       <c r="L86" s="19"/>
       <c r="M86" s="19"/>
     </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:F2"/>
